--- a/jpcore-r4/develop/StructureDefinition-jp-medicationstatement-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationstatement-injection.xlsx
@@ -656,8 +656,7 @@
     <t>What medication was supplied　医薬品</t>
   </si>
   <si>
-    <t>Identifies the medication that was administered. This is either a link to a resource representing the details of the medication or a simple attribute carrying a code that identifies the medication from a known list of medications.
-投与された薬剤を識別する。既知の薬のリストから薬を識別するコード情報を設定する。</t>
+    <t>医薬品の識別情報は必須でありmedicationReference.referenceが必ず存在しなければならない、JP Coreでは注射の医薬品情報は単一薬剤の場合も Medicationリソースとして記述し、medicationCodeableConceptは使用しない。参照するMedicationリソースは、MedicationRequest.contained属性に内包することが望ましいが、外部参照としても良い。</t>
   </si>
   <si>
     <t>If only a code is specified, then it needs to be a code for a specific product. If more information is required, then the use of the medication resource is recommended.  For example, if you require form or lot number, then you must reference the Medication resource.

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationstatement-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationstatement-injection.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-07-04</t>
+    <t>2024-11-18</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationstatement-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationstatement-injection.xlsx
@@ -1901,7 +1901,7 @@
     <t>シンボルの定義のソースについて明確である必要があります。 / Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
-    <t>urn:oid:1.2.392.200250.2.2.20.30</t>
+    <t>http://jami.jp/CodeSystem/MedicationMethodBasicUsage</t>
   </si>
   <si>
     <t>Coding.system</t>
@@ -2021,7 +2021,7 @@
     <t>投与⽅法に対応するJAMI 用法コード表基本用法2桁コード</t>
   </si>
   <si>
-    <t>投与⽅法に対応するJAMI 用法コード表基本用法2桁コードを識別するURI。２桁コードurn:oid:1.2.392.200250.2.2.20.40</t>
+    <t>投与⽅法に対応するJAMI 用法コード表基本用法2桁コードを識別するURI。２桁コードhttp://jami.jp/CodeSystem/MedicationUsage</t>
   </si>
   <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationMethodJAMIDetailUsage_VS</t>
@@ -2036,7 +2036,7 @@
     <t>MedicationStatement.dosage.method.coding:unitDigit2.system</t>
   </si>
   <si>
-    <t>urn:oid:1.2.392.200250.2.2.20.40</t>
+    <t>http://jami.jp/CodeSystem/MedicationMethodDetailUsage</t>
   </si>
   <si>
     <t>MedicationStatement.dosage.method.coding:unitDigit2.version</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationstatement-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationstatement-injection.xlsx
@@ -293,7 +293,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidまたはmeta.lastupdatedを持たないものとします / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -334,16 +334,16 @@
 </t>
   </si>
   <si>
-    <t>リソースに関するメタデータ / Metadata about the resource</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -469,7 +469,7 @@
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -1336,7 +1336,7 @@
     <t>Timing.repeat</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 tim-1:期間がある場合は、期間単位が必要です / if there's a duration, there needs to be duration units {duration.empty() or durationUnit.exists()}tim-2:期間がある場合、期間単位が必要です / if there's a period, there needs to be period units {period.empty() or periodUnit.exists()}tim-4:期間は非陰性価値です / duration SHALL be a non-negative value {duration.exists() implies duration &gt;= 0}tim-5:期間は非陰性の価値です / period SHALL be a non-negative value {period.exists() implies period &gt;= 0}tim-6:期間がある場合、期間がなければなりません / If there's a periodMax, there must be a period {periodMax.empty() or period.exists()}tim-7:Hurtermaxがある場合、期間がなければなりません / If there's a durationMax, there must be a duration {durationMax.empty() or duration.exists()}tim-8:countmaxがある場合、カウントが必要です / If there's a countMax, there must be a count {countMax.empty() or count.exists()}tim-9:オフセットがある場合、c、cm、cd、cvではなく（c、cvではない）存在する必要があります。 / If there's an offset, there must be a when (and not C, CM, CD, CV) {offset.empty() or (when.exists() and ((when in ('C' | 'CM' | 'CD' | 'CV')).not()))}tim-10:時間がある場合、いつ、またはその逆もありません / If there's a timeOfDay, there cannot be a when, or vice versa {timeOfDay.empty() or when.empty()}</t>
   </si>
   <si>
@@ -2123,7 +2123,7 @@
 </t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 qty-3:ユニットのコードが存在する場合、システムも存在するものとします / If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}sqty-1:コンパレータは、単純なQuantityで使用されません / The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
@@ -2184,7 +2184,7 @@
     <t>比率データタイプは、関係を数量と共通単位を使用して適切に表現できない場合にのみ、2つの数値の関係を表現するために使用する必要があります。分母値が「1」に固定されていることが知られている場合、比率ではなく数量を使用する必要があります。 / The Ratio datatype should only be used to express a relationship of two numbers if the relationship cannot be suitably expressed using a Quantity and a common unit.  Where the denominator value is known to be fixed to "1", Quantity should be used instead of Ratio.</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 rat-1:分子と分母の両方が存在するか、両方が存在します。両方が欠席している場合、いくつかの拡張が存在するものとします / Numerator and denominator SHALL both be present, or both are absent. If both are absent, there SHALL be some extension present {(numerator.empty() xor denominator.exists()) and (numerator.exists() or extension.exists())}</t>
   </si>
   <si>
@@ -2207,7 +2207,7 @@
     <t>時間の上限量、下限量の範囲を持っている。単位指定された数量を割り当てている。Low,Highの値は時間の単位当てはめる。</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 rng-2:存在する場合、低い値は高よりも低い値を持つものとします / If present, low SHALL have a lower value than high {low.empty() or high.empty() or (low &lt;= high)}</t>
   </si>
   <si>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationstatement-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationstatement-injection.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4414" uniqueCount="715">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4413" uniqueCount="705">
   <si>
     <t>Property</t>
   </si>
@@ -1068,7 +1068,7 @@
     <t>投薬声明の投与量に含まれる日付は、特定の用量の日付を反映しています。たとえば、「2016年11月1日から2016年11月3日まで、毎日1錠を服用し、2016年11月4日から2016年11月7日まで、毎日2錠を服用してください。」この特異性は、患者が標識容器を持ち込む場合、または薬物療法の声明が薬物療法に由来する場合にのみ居住することが予想されます。 / The dates included in the dosage on a Medication Statement reflect the dates for a given dose.  For example, "from November 1, 2016 to November 3, 2016, take one tablet daily and from November 4, 2016 to November 7, 2016, take two tablets daily."  It is expected that this specificity may only be populated where the patient brings in their labeled container or where the Medication Statement is derived from a MedicationRequest.</t>
   </si>
   <si>
-    <t>.outboundRelationship[typeCode=COMP].target[classCode=SBADM, moodCode=INT]</t>
+    <t>refer dosageInstruction mapping</t>
   </si>
   <si>
     <t>MedicationStatement.dosage.id</t>
@@ -1276,18 +1276,13 @@
     <t>投与タイミングを記録する。</t>
   </si>
   <si>
-    <t>複数回発生する可能性のあるイベントの発生について説明します。タイミングスケジュールは、イベントが発生することが予想または要求される時期を指定するために使用され、過去または進行中のイベントの概要を表すためにも使用できます。簡単にするために、タイミングコンポーネントの定義は「将来の」イベントとして表現されますが、そのようなコンポーネントは歴史的または進行中のイベントを説明するためにも使用できます。
-タイミングスケジュールは、イベントが発生したときのイベントおよび/または基準のリストであり、構造化された形式またはコードとして表現できます。イベントと繰り返し仕様の両方が提供される場合、イベントのリストは、繰り返し構造の情報の解釈として理解されるべきです。 / Describes the occurrence of an event that may occur multiple times. Timing schedules are used for specifying when events are expected or requested to occur, and may also be used to represent the summary of a past or ongoing event.  For simplicity, the definitions of Timing components are expressed as 'future' events, but such components can also be used to describe historic or ongoing events.
-A Timing schedule can be a list of events and/or criteria for when the event happens, which can be expressed in a structured form and/or as a code. When both event and a repeating specification are provided, the list of events should be understood as an interpretation of the information in the repeat structure.</t>
+    <t>この属性は、Dosage.Textが入力されると予想される間、常に埋め込まれるとは限りません。両方が入力されている場合、Dosage.textはDosage.timingの内容を反映する必要があります。 / This attribute might not always be populated while the Dosage.text is expected to be populated.  If both are populated, then the Dosage.text should reflect the content of the Dosage.timing.</t>
   </si>
   <si>
     <t>患者に薬を与えるためのタイミングスケジュール。このデータ型により、さまざまな式が可能になります。たとえば、「8時間ごと」。"一日に三回";「2011年12月23日から10日間の朝食の1/2の1/2：」;「2013年10月15日、2013年10月17日、2013年11月1日」。時には、総量 /持続時間として表される場合、レートは期間を意味する場合があります（たとえば、500ml / 2時間は2時間の期間を意味します）。ただし、レートが期間（250ml/hour）を意味しない場合、期間にわたって注入を伝えるためにタイミング.repeat.durationが必要です。 / The timing schedule for giving the medication to the patient. This  data type allows many different expressions. For example: "Every 8 hours"; "Three times a day"; "1/2 an hour before breakfast for 10 days from 23-Dec 2011:"; "15 Oct 2013, 17 Oct 2013 and 1 Nov 2013".  Sometimes, a rate can imply duration when expressed as total volume / duration (e.g.  500mL/2 hours implies a duration of 2 hours).  However, when rate doesn't imply duration (e.g. 250mL/hour), then the timing.repeat.duration is needed to convey the infuse over time period.</t>
   </si>
   <si>
     <t>Dosage.timing</t>
-  </si>
-  <si>
-    <t>QSET&lt;TS&gt; (GTS)</t>
   </si>
   <si>
     <t>MedicationStatement.dosage.timing.id</t>
@@ -2119,18 +2114,7 @@
     <t>Dosage.doseAndRate.dose[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-qty-3:ユニットのコードが存在する場合、システムも存在するものとします / If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}sqty-1:コンパレータは、単純なQuantityで使用されません / The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
-  </si>
-  <si>
-    <t>PQ, IVL&lt;PQ&gt;, MO, CO, depending on the values</t>
-  </si>
-  <si>
-    <t>SN (see also Range) or CQ</t>
+    <t>RXO-2, RXE-3</t>
   </si>
   <si>
     <t>MedicationStatement.dosage.doseAndRate.rate[x]</t>
@@ -2178,19 +2162,6 @@
 </t>
   </si>
   <si>
-    <t>単位時間内での薬剤の容量</t>
-  </si>
-  <si>
-    <t>比率データタイプは、関係を数量と共通単位を使用して適切に表現できない場合にのみ、2つの数値の関係を表現するために使用する必要があります。分母値が「1」に固定されていることが知られている場合、比率ではなく数量を使用する必要があります。 / The Ratio datatype should only be used to express a relationship of two numbers if the relationship cannot be suitably expressed using a Quantity and a common unit.  Where the denominator value is known to be fixed to "1", Quantity should be used instead of Ratio.</t>
-  </si>
-  <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-rat-1:分子と分母の両方が存在するか、両方が存在します。両方が欠席している場合、いくつかの拡張が存在するものとします / Numerator and denominator SHALL both be present, or both are absent. If both are absent, there SHALL be some extension present {(numerator.empty() xor denominator.exists()) and (numerator.exists() or extension.exists())}</t>
-  </si>
-  <si>
-    <t>RTO</t>
-  </si>
-  <si>
     <t>MedicationStatement.dosage.doseAndRate.rate[x]:rateRange</t>
   </si>
   <si>
@@ -2201,22 +2172,6 @@
 </t>
   </si>
   <si>
-    <t>範囲指定された時間の上限下限</t>
-  </si>
-  <si>
-    <t>時間の上限量、下限量の範囲を持っている。単位指定された数量を割り当てている。Low,Highの値は時間の単位当てはめる。</t>
-  </si>
-  <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-rng-2:存在する場合、低い値は高よりも低い値を持つものとします / If present, low SHALL have a lower value than high {low.empty() or high.empty() or (low &lt;= high)}</t>
-  </si>
-  <si>
-    <t>IVL&lt;QTY[not(type="TS")]&gt; [lowClosed="true" and highClosed="true"]or URG&lt;QTY[not(type="TS")]&gt;</t>
-  </si>
-  <si>
-    <t>NR and also possibly SN (but see also quantity)</t>
-  </si>
-  <si>
     <t>MedicationStatement.dosage.doseAndRate.rate[x]:rateQuantity</t>
   </si>
   <si>
@@ -2230,34 +2185,43 @@
     <t>投与速度(流量)を指定する単位は流量を表す単位（e.g. 量/時間)を指定する</t>
   </si>
   <si>
-    <t>使用のコンテキストは、これがどのような量であるか、したがってどのようなユニットを使用できるかを頻繁に定義する場合があります。使用のコンテキストは、コンパレータの値を制限する場合もあります。 / The context of use may frequently define what kind of quantity this is and therefore what kind of units can be used. The context of use may also restrict the values for the comparator.</t>
-  </si>
-  <si>
     <t>MedicationStatement.dosage.maxDosePerPeriod</t>
   </si>
   <si>
     <t>単位時間当たりの投薬量の上限</t>
   </si>
   <si>
+    <t>これは、上限があるときに投与量の補助として使用することを目的としています。たとえば、「4時間ごとに最大8時間あたり2錠」。 / This is intended for use as an adjunct to the dosage when there is an upper cap.  For example "2 tablets every 4 hours to a maximum of 8/day".</t>
+  </si>
+  <si>
     <t>期間にわたって被験者に投与される可能性のある治療物質の最大総量。たとえば、24時間で1000mg。 / The maximum total quantity of a therapeutic substance that may be administered to a subject over the period of time.  For example, 1000mg in 24 hours.</t>
   </si>
   <si>
     <t>Dosage.maxDosePerPeriod</t>
   </si>
   <si>
+    <t>.maxDoseQuantity</t>
+  </si>
+  <si>
+    <t>RXO-23, RXE-19</t>
+  </si>
+  <si>
     <t>MedicationStatement.dosage.maxDosePerAdministration</t>
   </si>
   <si>
     <t>1回あたりの投薬量の上限</t>
   </si>
   <si>
-    <t>薬剤に関する簡易的な数量と単位を定めている。ValueおよびCodeを必須とし、comparatorは記述不可。単位についてはMERIT9医薬品単位略号の利用を推進している。(**SHOULD**)</t>
+    <t>これは、上限があるときに投与量の補助として使用することを目的としています。たとえば、5〜10分間で1.5 mg/m2（最大2 mg）IVなどの最大量の体積領域に関連する用量に関連する用量は、1.5 mg/m2、最大2 mgのDosequantityになります。 / This is intended for use as an adjunct to the dosage when there is an upper cap.  For example, a body surface area related dose with a maximum amount, such as 1.5 mg/m2 (maximum 2 mg) IV over 5 – 10 minutes would have doseQuantity of 1.5 mg/m2 and maxDosePerAdministration of 2 mg.</t>
   </si>
   <si>
     <t>投与ごとの被験者に投与される可能性のある治療物質の最大総量。 / The maximum total quantity of a therapeutic substance that may be administered to a subject per administration.</t>
   </si>
   <si>
     <t>Dosage.maxDosePerAdministration</t>
+  </si>
+  <si>
+    <t>not supported</t>
   </si>
   <si>
     <t>MedicationStatement.dosage.maxDosePerLifetime</t>
@@ -8120,7 +8084,7 @@
         <v>79</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
         <v>391</v>
@@ -8202,21 +8166,21 @@
         <v>79</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>397</v>
+        <v>227</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>133</v>
+        <v>79</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8325,10 +8289,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8439,10 +8403,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8555,10 +8519,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8584,14 +8548,14 @@
         <v>249</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>403</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>79</v>
@@ -8640,7 +8604,7 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8658,7 +8622,7 @@
         <v>79</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>79</v>
@@ -8669,10 +8633,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8695,17 +8659,17 @@
         <v>91</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>79</v>
@@ -8754,7 +8718,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8766,13 +8730,13 @@
         <v>79</v>
       </c>
       <c r="AJ54" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL54" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="AK54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL54" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>79</v>
@@ -8783,10 +8747,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8895,10 +8859,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9009,10 +8973,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9035,13 +8999,13 @@
         <v>91</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="L57" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="M57" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9092,7 +9056,7 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9110,7 +9074,7 @@
         <v>79</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>79</v>
@@ -9121,10 +9085,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9147,19 +9111,19 @@
         <v>91</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="L58" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="M58" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="N58" t="s" s="2">
+      <c r="O58" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>79</v>
@@ -9208,7 +9172,7 @@
         <v>79</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9226,7 +9190,7 @@
         <v>79</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>79</v>
@@ -9237,10 +9201,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9263,16 +9227,16 @@
         <v>91</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>434</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9322,7 +9286,7 @@
         <v>79</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9340,7 +9304,7 @@
         <v>79</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>79</v>
@@ -9351,10 +9315,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9377,19 +9341,19 @@
         <v>91</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="M60" t="s" s="2">
+      <c r="N60" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="N60" t="s" s="2">
+      <c r="O60" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>79</v>
@@ -9438,7 +9402,7 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9456,7 +9420,7 @@
         <v>79</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>79</v>
@@ -9467,10 +9431,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9493,19 +9457,19 @@
         <v>91</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="M61" t="s" s="2">
-        <v>446</v>
-      </c>
       <c r="N61" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="O61" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>79</v>
@@ -9554,7 +9518,7 @@
         <v>79</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9572,7 +9536,7 @@
         <v>79</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>79</v>
@@ -9583,10 +9547,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9612,10 +9576,10 @@
         <v>110</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="N62" t="s" s="2">
         <v>388</v>
@@ -9647,28 +9611,28 @@
         <v>173</v>
       </c>
       <c r="Y62" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="Z62" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="Z62" t="s" s="2">
+      <c r="AA62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF62" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="AA62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9686,7 +9650,7 @@
         <v>79</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>79</v>
@@ -9697,10 +9661,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9723,68 +9687,68 @@
         <v>91</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q63" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="R63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF63" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="R63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9802,7 +9766,7 @@
         <v>79</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>79</v>
@@ -9813,10 +9777,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9839,16 +9803,16 @@
         <v>91</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="M64" t="s" s="2">
-        <v>463</v>
-      </c>
       <c r="N64" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9898,7 +9862,7 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9916,7 +9880,7 @@
         <v>79</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>79</v>
@@ -9927,10 +9891,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9953,16 +9917,16 @@
         <v>91</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="M65" t="s" s="2">
+      <c r="N65" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>468</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10012,7 +9976,7 @@
         <v>79</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10030,7 +9994,7 @@
         <v>79</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>79</v>
@@ -10041,10 +10005,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10067,16 +10031,16 @@
         <v>91</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>473</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10126,7 +10090,7 @@
         <v>79</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10144,7 +10108,7 @@
         <v>79</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>79</v>
@@ -10155,10 +10119,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10184,10 +10148,10 @@
         <v>110</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>388</v>
@@ -10219,11 +10183,11 @@
         <v>173</v>
       </c>
       <c r="Y67" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="Z67" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="Z67" t="s" s="2">
-        <v>452</v>
-      </c>
       <c r="AA67" t="s" s="2">
         <v>79</v>
       </c>
@@ -10240,7 +10204,7 @@
         <v>79</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10258,7 +10222,7 @@
         <v>79</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>79</v>
@@ -10269,10 +10233,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10298,13 +10262,13 @@
         <v>110</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>479</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="N68" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>481</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10334,25 +10298,25 @@
       </c>
       <c r="Y68" s="2"/>
       <c r="Z68" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF68" t="s" s="2">
         <v>482</v>
-      </c>
-      <c r="AA68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>483</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10381,10 +10345,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10407,16 +10371,16 @@
         <v>91</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="L69" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="L69" t="s" s="2">
+      <c r="M69" t="s" s="2">
         <v>486</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="N69" t="s" s="2">
         <v>487</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>488</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10466,7 +10430,7 @@
         <v>79</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10495,10 +10459,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10524,16 +10488,16 @@
         <v>110</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="N70" t="s" s="2">
+      <c r="O70" t="s" s="2">
         <v>493</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>494</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>79</v>
@@ -10561,28 +10525,28 @@
         <v>173</v>
       </c>
       <c r="Y70" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="Z70" t="s" s="2">
         <v>495</v>
       </c>
-      <c r="Z70" t="s" s="2">
+      <c r="AA70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF70" t="s" s="2">
         <v>496</v>
-      </c>
-      <c r="AA70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF70" t="s" s="2">
-        <v>497</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10600,7 +10564,7 @@
         <v>79</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>79</v>
@@ -10611,10 +10575,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10637,16 +10601,16 @@
         <v>91</v>
       </c>
       <c r="K71" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="L71" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="L71" t="s" s="2">
+      <c r="M71" t="s" s="2">
         <v>501</v>
       </c>
-      <c r="M71" t="s" s="2">
-        <v>502</v>
-      </c>
       <c r="N71" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10696,7 +10660,7 @@
         <v>79</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10714,7 +10678,7 @@
         <v>79</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>79</v>
@@ -10725,10 +10689,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10754,13 +10718,13 @@
         <v>180</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="N72" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>508</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10790,25 +10754,25 @@
       </c>
       <c r="Y72" s="2"/>
       <c r="Z72" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF72" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>510</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10826,7 +10790,7 @@
         <v>79</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>79</v>
@@ -10837,10 +10801,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10863,16 +10827,16 @@
         <v>91</v>
       </c>
       <c r="K73" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="L73" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="L73" t="s" s="2">
+      <c r="M73" t="s" s="2">
         <v>514</v>
       </c>
-      <c r="M73" t="s" s="2">
+      <c r="N73" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>516</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10922,7 +10886,7 @@
         <v>79</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10940,21 +10904,21 @@
         <v>79</v>
       </c>
       <c r="AL73" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN73" t="s" s="2">
         <v>518</v>
-      </c>
-      <c r="AM73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN73" t="s" s="2">
-        <v>519</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10980,16 +10944,16 @@
         <v>180</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="N74" t="s" s="2">
+      <c r="O74" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>79</v>
@@ -11018,25 +10982,25 @@
       </c>
       <c r="Y74" s="2"/>
       <c r="Z74" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF74" t="s" s="2">
         <v>525</v>
-      </c>
-      <c r="AA74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>526</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11054,21 +11018,21 @@
         <v>79</v>
       </c>
       <c r="AL74" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN74" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>528</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11177,10 +11141,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11291,13 +11255,13 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="C77" t="s" s="2">
         <v>531</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="C77" t="s" s="2">
-        <v>532</v>
       </c>
       <c r="D77" t="s" s="2">
         <v>79</v>
@@ -11319,13 +11283,13 @@
         <v>79</v>
       </c>
       <c r="K77" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="L77" t="s" s="2">
         <v>533</v>
       </c>
-      <c r="L77" t="s" s="2">
+      <c r="M77" t="s" s="2">
         <v>534</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>535</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11405,13 +11369,13 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="C78" t="s" s="2">
         <v>536</v>
-      </c>
-      <c r="B78" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="C78" t="s" s="2">
-        <v>537</v>
       </c>
       <c r="D78" t="s" s="2">
         <v>79</v>
@@ -11433,13 +11397,13 @@
         <v>79</v>
       </c>
       <c r="K78" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="L78" t="s" s="2">
         <v>538</v>
       </c>
-      <c r="L78" t="s" s="2">
+      <c r="M78" t="s" s="2">
         <v>539</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>540</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11519,10 +11483,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11548,7 +11512,7 @@
         <v>294</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="M79" t="s" s="2">
         <v>296</v>
@@ -11635,10 +11599,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11751,10 +11715,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11780,16 +11744,16 @@
         <v>180</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="N81" t="s" s="2">
         <v>545</v>
       </c>
-      <c r="M81" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="N81" t="s" s="2">
+      <c r="O81" t="s" s="2">
         <v>546</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>547</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>79</v>
@@ -11818,25 +11782,25 @@
       </c>
       <c r="Y81" s="2"/>
       <c r="Z81" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF81" t="s" s="2">
         <v>548</v>
-      </c>
-      <c r="AA81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF81" t="s" s="2">
-        <v>549</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -11854,21 +11818,21 @@
         <v>79</v>
       </c>
       <c r="AL81" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN81" t="s" s="2">
         <v>550</v>
-      </c>
-      <c r="AM81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>551</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11977,10 +11941,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12091,13 +12055,13 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="C84" t="s" s="2">
         <v>554</v>
-      </c>
-      <c r="B84" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="C84" t="s" s="2">
-        <v>555</v>
       </c>
       <c r="D84" t="s" s="2">
         <v>79</v>
@@ -12119,13 +12083,13 @@
         <v>79</v>
       </c>
       <c r="K84" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="L84" t="s" s="2">
         <v>556</v>
       </c>
-      <c r="L84" t="s" s="2">
+      <c r="M84" t="s" s="2">
         <v>557</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>558</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -12205,10 +12169,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12234,7 +12198,7 @@
         <v>294</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="M85" t="s" s="2">
         <v>296</v>
@@ -12321,10 +12285,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12437,10 +12401,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12466,16 +12430,16 @@
         <v>180</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="M87" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="N87" t="s" s="2">
         <v>562</v>
       </c>
-      <c r="M87" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="N87" t="s" s="2">
+      <c r="O87" t="s" s="2">
         <v>563</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>564</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>79</v>
@@ -12503,28 +12467,28 @@
         <v>184</v>
       </c>
       <c r="Y87" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="Z87" t="s" s="2">
         <v>565</v>
       </c>
-      <c r="Z87" t="s" s="2">
+      <c r="AA87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF87" t="s" s="2">
         <v>566</v>
-      </c>
-      <c r="AA87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF87" t="s" s="2">
-        <v>567</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12542,21 +12506,21 @@
         <v>79</v>
       </c>
       <c r="AL87" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN87" t="s" s="2">
         <v>568</v>
-      </c>
-      <c r="AM87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN87" t="s" s="2">
-        <v>569</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12665,10 +12629,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12779,13 +12743,13 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="C90" t="s" s="2">
         <v>572</v>
-      </c>
-      <c r="B90" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="C90" t="s" s="2">
-        <v>573</v>
       </c>
       <c r="D90" t="s" s="2">
         <v>79</v>
@@ -12807,13 +12771,13 @@
         <v>79</v>
       </c>
       <c r="K90" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="L90" t="s" s="2">
         <v>574</v>
       </c>
-      <c r="L90" t="s" s="2">
+      <c r="M90" t="s" s="2">
         <v>575</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>576</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -12893,10 +12857,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12922,7 +12886,7 @@
         <v>294</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="M91" t="s" s="2">
         <v>296</v>
@@ -12968,7 +12932,7 @@
         <v>79</v>
       </c>
       <c r="AB91" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="AC91" s="2"/>
       <c r="AD91" t="s" s="2">
@@ -13007,13 +12971,13 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="C92" t="s" s="2">
         <v>579</v>
-      </c>
-      <c r="B92" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="C92" t="s" s="2">
-        <v>580</v>
       </c>
       <c r="D92" t="s" s="2">
         <v>79</v>
@@ -13038,16 +13002,16 @@
         <v>294</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>581</v>
       </c>
-      <c r="M92" t="s" s="2">
+      <c r="N92" t="s" s="2">
         <v>582</v>
       </c>
-      <c r="N92" t="s" s="2">
+      <c r="O92" t="s" s="2">
         <v>583</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>584</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>79</v>
@@ -13076,7 +13040,7 @@
       </c>
       <c r="Y92" s="2"/>
       <c r="Z92" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>79</v>
@@ -13123,10 +13087,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="B93" t="s" s="2">
         <v>586</v>
-      </c>
-      <c r="B93" t="s" s="2">
-        <v>587</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13235,10 +13199,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="B94" t="s" s="2">
         <v>588</v>
-      </c>
-      <c r="B94" t="s" s="2">
-        <v>589</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13349,10 +13313,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="B95" t="s" s="2">
         <v>590</v>
-      </c>
-      <c r="B95" t="s" s="2">
-        <v>591</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13378,65 +13342,65 @@
         <v>104</v>
       </c>
       <c r="L95" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="M95" t="s" s="2">
         <v>592</v>
       </c>
-      <c r="M95" t="s" s="2">
+      <c r="N95" t="s" s="2">
         <v>593</v>
       </c>
-      <c r="N95" t="s" s="2">
+      <c r="O95" t="s" s="2">
         <v>594</v>
-      </c>
-      <c r="O95" t="s" s="2">
-        <v>595</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q95" s="2"/>
       <c r="R95" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="S95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF95" t="s" s="2">
         <v>596</v>
-      </c>
-      <c r="S95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF95" t="s" s="2">
-        <v>597</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13454,21 +13418,21 @@
         <v>79</v>
       </c>
       <c r="AL95" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="AM95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN95" t="s" s="2">
         <v>598</v>
-      </c>
-      <c r="AM95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN95" t="s" s="2">
-        <v>599</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="B96" t="s" s="2">
         <v>600</v>
-      </c>
-      <c r="B96" t="s" s="2">
-        <v>601</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13494,13 +13458,13 @@
         <v>236</v>
       </c>
       <c r="L96" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="M96" t="s" s="2">
         <v>602</v>
       </c>
-      <c r="M96" t="s" s="2">
+      <c r="N96" t="s" s="2">
         <v>603</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>604</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -13550,7 +13514,7 @@
         <v>79</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -13568,21 +13532,21 @@
         <v>79</v>
       </c>
       <c r="AL96" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="AM96" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN96" t="s" s="2">
         <v>606</v>
-      </c>
-      <c r="AM96" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN96" t="s" s="2">
-        <v>607</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="B97" t="s" s="2">
         <v>608</v>
-      </c>
-      <c r="B97" t="s" s="2">
-        <v>609</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13608,14 +13572,14 @@
         <v>110</v>
       </c>
       <c r="L97" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="M97" t="s" s="2">
         <v>610</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>611</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>79</v>
@@ -13664,7 +13628,7 @@
         <v>79</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -13682,21 +13646,21 @@
         <v>79</v>
       </c>
       <c r="AL97" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN97" t="s" s="2">
         <v>614</v>
-      </c>
-      <c r="AM97" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN97" t="s" s="2">
-        <v>615</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="B98" t="s" s="2">
         <v>616</v>
-      </c>
-      <c r="B98" t="s" s="2">
-        <v>617</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13722,14 +13686,14 @@
         <v>236</v>
       </c>
       <c r="L98" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="M98" t="s" s="2">
         <v>618</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>619</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>79</v>
@@ -13778,7 +13742,7 @@
         <v>79</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -13796,21 +13760,21 @@
         <v>79</v>
       </c>
       <c r="AL98" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="AM98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN98" t="s" s="2">
         <v>622</v>
-      </c>
-      <c r="AM98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN98" t="s" s="2">
-        <v>623</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="B99" t="s" s="2">
         <v>624</v>
-      </c>
-      <c r="B99" t="s" s="2">
-        <v>625</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13833,19 +13797,19 @@
         <v>91</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="L99" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="M99" t="s" s="2">
         <v>626</v>
       </c>
-      <c r="M99" t="s" s="2">
+      <c r="N99" t="s" s="2">
         <v>627</v>
       </c>
-      <c r="N99" t="s" s="2">
+      <c r="O99" t="s" s="2">
         <v>628</v>
-      </c>
-      <c r="O99" t="s" s="2">
-        <v>629</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>79</v>
@@ -13894,7 +13858,7 @@
         <v>79</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -13912,24 +13876,24 @@
         <v>79</v>
       </c>
       <c r="AL99" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="AM99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN99" t="s" s="2">
         <v>631</v>
-      </c>
-      <c r="AM99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN99" t="s" s="2">
-        <v>632</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="C100" t="s" s="2">
         <v>633</v>
-      </c>
-      <c r="B100" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="C100" t="s" s="2">
-        <v>634</v>
       </c>
       <c r="D100" t="s" s="2">
         <v>79</v>
@@ -13954,16 +13918,16 @@
         <v>294</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="M100" t="s" s="2">
         <v>635</v>
       </c>
-      <c r="M100" t="s" s="2">
-        <v>636</v>
-      </c>
       <c r="N100" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="O100" t="s" s="2">
         <v>583</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>584</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>79</v>
@@ -13992,7 +13956,7 @@
       </c>
       <c r="Y100" s="2"/>
       <c r="Z100" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>79</v>
@@ -14039,10 +14003,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14151,10 +14115,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14265,10 +14229,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14294,23 +14258,23 @@
         <v>104</v>
       </c>
       <c r="L103" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="M103" t="s" s="2">
         <v>592</v>
       </c>
-      <c r="M103" t="s" s="2">
+      <c r="N103" t="s" s="2">
         <v>593</v>
       </c>
-      <c r="N103" t="s" s="2">
+      <c r="O103" t="s" s="2">
         <v>594</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>595</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q103" s="2"/>
       <c r="R103" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S103" t="s" s="2">
         <v>79</v>
@@ -14352,7 +14316,7 @@
         <v>79</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14370,21 +14334,21 @@
         <v>79</v>
       </c>
       <c r="AL103" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="AM103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN103" t="s" s="2">
         <v>598</v>
-      </c>
-      <c r="AM103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN103" t="s" s="2">
-        <v>599</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14410,13 +14374,13 @@
         <v>236</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="M104" t="s" s="2">
         <v>602</v>
       </c>
-      <c r="M104" t="s" s="2">
+      <c r="N104" t="s" s="2">
         <v>603</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>604</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -14466,7 +14430,7 @@
         <v>79</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -14484,21 +14448,21 @@
         <v>79</v>
       </c>
       <c r="AL104" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="AM104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN104" t="s" s="2">
         <v>606</v>
-      </c>
-      <c r="AM104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN104" t="s" s="2">
-        <v>607</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14524,14 +14488,14 @@
         <v>110</v>
       </c>
       <c r="L105" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="M105" t="s" s="2">
         <v>610</v>
-      </c>
-      <c r="M105" t="s" s="2">
-        <v>611</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>79</v>
@@ -14580,7 +14544,7 @@
         <v>79</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -14598,21 +14562,21 @@
         <v>79</v>
       </c>
       <c r="AL105" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="AM105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN105" t="s" s="2">
         <v>614</v>
-      </c>
-      <c r="AM105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN105" t="s" s="2">
-        <v>615</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14638,14 +14602,14 @@
         <v>236</v>
       </c>
       <c r="L106" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="M106" t="s" s="2">
         <v>618</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>619</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>79</v>
@@ -14694,7 +14658,7 @@
         <v>79</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -14712,21 +14676,21 @@
         <v>79</v>
       </c>
       <c r="AL106" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="AM106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN106" t="s" s="2">
         <v>622</v>
-      </c>
-      <c r="AM106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN106" t="s" s="2">
-        <v>623</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14749,19 +14713,19 @@
         <v>91</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="L107" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="M107" t="s" s="2">
         <v>626</v>
       </c>
-      <c r="M107" t="s" s="2">
+      <c r="N107" t="s" s="2">
         <v>627</v>
       </c>
-      <c r="N107" t="s" s="2">
+      <c r="O107" t="s" s="2">
         <v>628</v>
-      </c>
-      <c r="O107" t="s" s="2">
-        <v>629</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>79</v>
@@ -14810,7 +14774,7 @@
         <v>79</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -14828,21 +14792,21 @@
         <v>79</v>
       </c>
       <c r="AL107" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="AM107" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN107" t="s" s="2">
         <v>631</v>
-      </c>
-      <c r="AM107" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN107" t="s" s="2">
-        <v>632</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14955,10 +14919,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14981,13 +14945,13 @@
         <v>91</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="L109" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="M109" t="s" s="2">
         <v>648</v>
-      </c>
-      <c r="M109" t="s" s="2">
-        <v>649</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -15038,7 +15002,7 @@
         <v>79</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15062,15 +15026,15 @@
         <v>79</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15179,10 +15143,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15293,10 +15257,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C112" t="s" s="2">
         <v>352</v>
@@ -15407,10 +15371,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15436,16 +15400,16 @@
         <v>180</v>
       </c>
       <c r="L113" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="M113" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="N113" t="s" s="2">
         <v>656</v>
       </c>
-      <c r="M113" t="s" s="2">
-        <v>656</v>
-      </c>
-      <c r="N113" t="s" s="2">
+      <c r="O113" t="s" s="2">
         <v>657</v>
-      </c>
-      <c r="O113" t="s" s="2">
-        <v>658</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>79</v>
@@ -15474,25 +15438,25 @@
       </c>
       <c r="Y113" s="2"/>
       <c r="Z113" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="AA113" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB113" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC113" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD113" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE113" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF113" t="s" s="2">
         <v>659</v>
-      </c>
-      <c r="AA113" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB113" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC113" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD113" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE113" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF113" t="s" s="2">
-        <v>660</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -15516,15 +15480,15 @@
         <v>79</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15544,22 +15508,22 @@
         <v>79</v>
       </c>
       <c r="J114" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K114" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="L114" t="s" s="2">
         <v>663</v>
       </c>
-      <c r="L114" t="s" s="2">
+      <c r="M114" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="N114" t="s" s="2">
         <v>664</v>
       </c>
-      <c r="M114" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="N114" t="s" s="2">
+      <c r="O114" t="s" s="2">
         <v>665</v>
-      </c>
-      <c r="O114" t="s" s="2">
-        <v>666</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>79</v>
@@ -15608,7 +15572,7 @@
         <v>79</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -15617,30 +15581,30 @@
         <v>90</v>
       </c>
       <c r="AI114" t="s" s="2">
-        <v>668</v>
+        <v>79</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>669</v>
+        <v>102</v>
       </c>
       <c r="AK114" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>670</v>
+        <v>567</v>
       </c>
       <c r="AM114" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>671</v>
+        <v>667</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15663,19 +15627,19 @@
         <v>91</v>
       </c>
       <c r="K115" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="L115" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="M115" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="N115" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="O115" t="s" s="2">
         <v>673</v>
-      </c>
-      <c r="L115" t="s" s="2">
-        <v>674</v>
-      </c>
-      <c r="M115" t="s" s="2">
-        <v>675</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>676</v>
-      </c>
-      <c r="O115" t="s" s="2">
-        <v>677</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>79</v>
@@ -15719,10 +15683,10 @@
         <v>79</v>
       </c>
       <c r="AE115" t="s" s="2">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -15740,24 +15704,24 @@
         <v>79</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="AM115" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>681</v>
+        <v>677</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="C116" t="s" s="2">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="D116" t="s" s="2">
         <v>79</v>
@@ -15776,22 +15740,22 @@
         <v>79</v>
       </c>
       <c r="J116" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>685</v>
+        <v>670</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>685</v>
+        <v>671</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>686</v>
+        <v>672</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>79</v>
@@ -15840,7 +15804,7 @@
         <v>79</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -15849,33 +15813,33 @@
         <v>90</v>
       </c>
       <c r="AI116" t="s" s="2">
-        <v>668</v>
+        <v>79</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>687</v>
+        <v>102</v>
       </c>
       <c r="AK116" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>688</v>
+        <v>676</v>
       </c>
       <c r="AM116" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>133</v>
+        <v>677</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>689</v>
+        <v>681</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>690</v>
+        <v>682</v>
       </c>
       <c r="D117" t="s" s="2">
         <v>79</v>
@@ -15894,22 +15858,22 @@
         <v>79</v>
       </c>
       <c r="J117" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>691</v>
+        <v>683</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>692</v>
+        <v>670</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>692</v>
+        <v>671</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>693</v>
+        <v>672</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>79</v>
@@ -15958,7 +15922,7 @@
         <v>79</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -15967,33 +15931,33 @@
         <v>90</v>
       </c>
       <c r="AI117" t="s" s="2">
-        <v>668</v>
+        <v>79</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>694</v>
+        <v>102</v>
       </c>
       <c r="AK117" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>695</v>
+        <v>676</v>
       </c>
       <c r="AM117" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>696</v>
+        <v>677</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>697</v>
+        <v>684</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>698</v>
+        <v>685</v>
       </c>
       <c r="D118" t="s" s="2">
         <v>79</v>
@@ -16012,22 +15976,22 @@
         <v>79</v>
       </c>
       <c r="J118" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>699</v>
+        <v>686</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>700</v>
+        <v>687</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>700</v>
+        <v>687</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>701</v>
+        <v>672</v>
       </c>
       <c r="O118" t="s" s="2">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>79</v>
@@ -16076,7 +16040,7 @@
         <v>79</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -16085,30 +16049,30 @@
         <v>90</v>
       </c>
       <c r="AI118" t="s" s="2">
-        <v>668</v>
+        <v>79</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>669</v>
+        <v>102</v>
       </c>
       <c r="AK118" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="AM118" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>671</v>
+        <v>677</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>702</v>
+        <v>688</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>702</v>
+        <v>688</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16128,22 +16092,22 @@
         <v>79</v>
       </c>
       <c r="J119" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>703</v>
+        <v>689</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>703</v>
+        <v>689</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="O119" t="s" s="2">
-        <v>704</v>
+        <v>691</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>79</v>
@@ -16192,7 +16156,7 @@
         <v>79</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>705</v>
+        <v>692</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -16201,30 +16165,30 @@
         <v>90</v>
       </c>
       <c r="AI119" t="s" s="2">
-        <v>668</v>
+        <v>79</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>687</v>
+        <v>102</v>
       </c>
       <c r="AK119" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>688</v>
+        <v>693</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>133</v>
+        <v>694</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>706</v>
+        <v>695</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>706</v>
+        <v>695</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16244,22 +16208,22 @@
         <v>79</v>
       </c>
       <c r="J120" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>707</v>
+        <v>696</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>707</v>
+        <v>696</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>708</v>
+        <v>697</v>
       </c>
       <c r="O120" t="s" s="2">
-        <v>709</v>
+        <v>698</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>79</v>
@@ -16308,7 +16272,7 @@
         <v>79</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>710</v>
+        <v>699</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -16317,30 +16281,30 @@
         <v>90</v>
       </c>
       <c r="AI120" t="s" s="2">
-        <v>668</v>
+        <v>79</v>
       </c>
       <c r="AJ120" t="s" s="2">
-        <v>669</v>
+        <v>102</v>
       </c>
       <c r="AK120" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>670</v>
+        <v>700</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>671</v>
+        <v>79</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>711</v>
+        <v>701</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>711</v>
+        <v>701</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16360,22 +16324,20 @@
         <v>79</v>
       </c>
       <c r="J121" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>712</v>
+        <v>702</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>712</v>
-      </c>
-      <c r="N121" t="s" s="2">
-        <v>708</v>
-      </c>
+        <v>702</v>
+      </c>
+      <c r="N121" s="2"/>
       <c r="O121" t="s" s="2">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>79</v>
@@ -16424,7 +16386,7 @@
         <v>79</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>714</v>
+        <v>704</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -16433,22 +16395,22 @@
         <v>90</v>
       </c>
       <c r="AI121" t="s" s="2">
-        <v>668</v>
+        <v>79</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>669</v>
+        <v>102</v>
       </c>
       <c r="AK121" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>670</v>
+        <v>700</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>671</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationstatement-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationstatement-injection.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-dev</t>
+    <t>1.3.0-dev</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-18</t>
+    <t>2024-12-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationstatement-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationstatement-injection.xlsx
@@ -293,7 +293,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -716,10 +716,10 @@
 </t>
   </si>
   <si>
-    <t>薬物測定に関連する遭遇 /エピソード / Encounter / Episode associated with MedicationStatement</t>
-  </si>
-  <si>
-    <t>この薬物測定のコンテキストを確立する遭遇またはケアのエピソード。 / The encounter or episode of care that establishes the context for this MedicationStatement.</t>
+    <t>薬物測定に関連するEnounter /エピソード / Encounter / Episode associated with MedicationStatement</t>
+  </si>
+  <si>
+    <t>この薬物測定のコンテキストを確立するEnounterまたはケアのエピソード。 / The encounter or episode of care that establishes the context for this MedicationStatement.</t>
   </si>
   <si>
     <t>Event.context</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationstatement-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationstatement-injection.xlsx
@@ -563,7 +563,7 @@
     <t>MedicationStatement.status</t>
   </si>
   <si>
-    <t>アクティブ|完了|エラーに入った|意図した|停止|オンホールド|不明|非テイク / active | completed | entered-in-error | intended | stopped | on-hold | unknown | not-taken</t>
+    <t>アクティブ | 完了 | エラー入力 | 意図的 | 停止 | 保留 | 不明 | 未取得 / active | completed | entered-in-error | intended | stopped | on-hold | unknown | not-taken</t>
   </si>
   <si>
     <t>服薬状況のを示す。コード表： http://hl7.org/fhir/CodeSystem/medication-statement-status

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationstatement-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationstatement-injection.xlsx
@@ -2542,17 +2542,17 @@
   <dimension ref="A1:AN121"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="64.5078125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="54.859375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="17.10546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="55.3046875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="47.03125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="14.6640625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="98.48828125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="84.4375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2561,26 +2561,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="188.5859375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="77.19140625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="38.25" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="161.6796875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="66.17578125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="32.79296875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="140.73046875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="45.6171875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="120.65234375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="39.109375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11385,7 +11385,7 @@
         <v>80</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>79</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationstatement-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationstatement-injection.xlsx
@@ -1717,7 +1717,7 @@
     <t>bodySite</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {bodySite}
+    <t xml:space="preserve">Extension {bodySite|5.2.0}
 </t>
   </si>
   <si>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationstatement-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationstatement-injection.xlsx
@@ -388,7 +388,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -519,7 +519,7 @@
     <t>MedicationStatement.basedOn</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationRequest|CarePlan|ServiceRequest)
+    <t xml:space="preserve">Reference(MedicationRequest|4.0.1|CarePlan|4.0.1|ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -541,7 +541,7 @@
     <t>MedicationStatement.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Observation)
+    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|MedicationDispense|4.0.1|MedicationStatement|4.0.1|Procedure|4.0.1|Observation|4.0.1)
 </t>
   </si>
   <si>
@@ -613,7 +613,7 @@
     <t>ステートメントのステータスの理由を示すコード化された概念。 / A coded concept indicating the reason for the status of the statement.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/reason-medication-status-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/reason-medication-status-codes|4.0.1</t>
   </si>
   <si>
     <t>Event.statusReason</t>
@@ -637,7 +637,7 @@
     <t>薬剤が含まれている場所を識別するコード化された概念は、薬物測定に含まれる場所が消費または投与されると予想されます。 / A coded concept identifying where the medication included in the MedicationStatement is expected to be consumed or administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-statement-category</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-statement-category|4.0.1</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=COMP].source[classCode=OBS, moodCode=EVN, code="type of medication usage"].value</t>
@@ -712,7 +712,7 @@
     <t>MedicationStatement.context</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter|EpisodeOfCare)
+    <t xml:space="preserve">Reference(Encounter|4.0.1|EpisodeOfCare|4.0.1)
 </t>
   </si>
   <si>
@@ -894,7 +894,7 @@
     <t>MedicationStatement.informationSource</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Practitioner|PractitionerRole|RelatedPerson|Organization)
+    <t xml:space="preserve">Reference(Patient|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1|RelatedPerson|4.0.1|Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -910,7 +910,7 @@
     <t>MedicationStatement.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -941,7 +941,7 @@
     <t>薬が服用されている理由を特定するコード化された概念。 / A coded concept identifying why the medication is being taken.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-code</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-code|4.0.1</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -1014,7 +1014,7 @@
     <t>MedicationStatement.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|Observation|DiagnosticReport)
+    <t xml:space="preserve">Reference(Condition|4.0.1|Observation|4.0.1|DiagnosticReport|4.0.1)
 </t>
   </si>
   <si>
@@ -1804,7 +1804,7 @@
     <t>薬が投与される手法を説明するコード化された概念。 / A coded concept describing the technique by which the medicine is administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/administration-method-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/administration-method-codes|4.0.1</t>
   </si>
   <si>
     <t>Dosage.method</t>
@@ -2121,7 +2121,7 @@
   </si>
   <si>
     <t>Ratio
-RangeQuantity {SimpleQuantity}</t>
+RangeQuantity {SimpleQuantity|4.0.1}</t>
   </si>
   <si>
     <t>薬剤の投与量速度</t>
@@ -2552,7 +2552,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="84.4375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="105.265625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationstatement-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationstatement-injection.xlsx
@@ -93,7 +93,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationstatement-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationstatement-injection.xlsx
@@ -1717,7 +1717,7 @@
     <t>bodySite</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {bodySite|5.2.0}
+    <t xml:space="preserve">Extension {bodySite|5.3.0}
 </t>
   </si>
   <si>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationstatement-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationstatement-injection.xlsx
@@ -1742,7 +1742,7 @@
     <t>投与経路</t>
   </si>
   <si>
-    <t>投与経路の一般的パターンに全てのターミノロジが適応しているわけではない。情報モデルはCodeableConceptではなく、直接Codingをを使用してテキストやコーディング、翻訳、そしてエレメントと事前条件、事後条件の関係について管理するためにその構造を提示する必要がある。  
+    <t>投与経路の一般的パターンに全てのターミノロジが適応しているわけではない。情報モデルはCodeableConceptではなく、直接`Coding`を使用してテキストや`Coding`、翻訳、そしてエレメントと事前条件、事後条件の関係について管理するためにその構造を提示する必要がある。
 【JP Core仕様】HL7表0162をベースにした投与経路コードを使用することが望ましいが、ローカルコードも使用可能。</t>
   </si>
   <si>
@@ -1857,7 +1857,7 @@
     <t>投与⽅法に対応するJAMI 用法コード表基本用法１桁コードを識別するURI。</t>
   </si>
   <si>
-    <t>コードは臨時で列記したものや、コードのリストからSNOMED CTのように公式に定義されたものまである（HL7 v3 core principle を参照)。FHIR自体ではコーディング規約を定めてはいないし、意味を暗示するために利用されない(SHALL NOT)。一般的に UserSelected = trueの場合には一つのコードシステムが使われる。</t>
+    <t>コードは臨時で列記したものや、コードのリストからSNOMED CTのように公式に定義されたものまである（HL7 v3 core principle を参照)。FHIR自体ではコード化に関する規約を定めてはいないし、意味を暗示するために利用されない(SHALL NOT)。一般的に UserSelected = trueの場合には一つのコードシステムが使われる。</t>
   </si>
   <si>
     <t>他のコードシステムへの変換や代替のコードシステムを使ってエンコードしてもよい。</t>
@@ -2079,7 +2079,7 @@
     <t>力価区分</t>
   </si>
   <si>
-    <t>投与速度・量の一般的パターンに全てのターミノロジが適応しているわけではない。情報モデルはCodeableConceptではなく、直接Codingをを使用してテキストやコーディング、翻訳、そしてエレメントと事前条件、事後条件の関係について管理するためにその構造を提示する必要がある。</t>
+    <t>投与速度・量の一般的パターンに全てのターミノロジが適応しているわけではない。情報モデルはCodeableConceptではなく、直接`Coding`を使用してテキストや`Coding`、翻訳、そしてエレメントと事前条件、事後条件の関係について管理するためにその構造を提示する必要がある。</t>
   </si>
   <si>
     <t>このtypeに値が指定されていなければ、"ordered"であることが想定される。</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationstatement-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationstatement-injection.xlsx
@@ -81,13 +81,13 @@
     <t>Description</t>
   </si>
   <si>
-    <t>このProfileは服薬状況を示すものであり，診療情報提供書や退院サマリーなどの他の文書と組み合わせて用いられる。</t>
+    <t>このProfileは服薬状況を示すものであり、診療情報提供書や退院サマリーなどの他の文書と組み合わせて用いられる。</t>
   </si>
   <si>
     <t>Purpose</t>
   </si>
   <si>
-    <t>このProfileは診療情報提供書や退院サマリーなどの医療文書内で服薬情報について記載するために用いられる。このResourceは薬剤処方や，調剤情報，薬剤投与実施情報としては用いられず，それぞれMedicationRequest, MedicationDispense, MedicationAdministrationが用いられる。</t>
+    <t>このProfileは診療情報提供書や退院サマリーなどの医療文書内で服薬情報について記載するために用いられる。このResourceは薬剤処方や、調剤情報、薬剤投与実施情報としては用いられず、それぞれMedicationRequest, MedicationDispense, MedicationAdministrationが用いられる。</t>
   </si>
   <si>
     <t>Copyright</t>
@@ -966,7 +966,7 @@
 </t>
   </si>
   <si>
-    <t>投与理由，対象疾患についてのコード</t>
+    <t>投与理由、対象疾患についてのコード</t>
   </si>
   <si>
     <t>用語システムによって定義されたコードへの参照。 / A reference to a code defined by a terminology system.</t>
@@ -1059,7 +1059,7 @@
 </t>
   </si>
   <si>
-    <t>この薬剤がどのように服用されたのか，服用すべきだったのかを示す情報</t>
+    <t>この薬剤がどのように服用されたのか、服用すべきだったのかを示す情報</t>
   </si>
   <si>
     <t>患者にこの薬剤がどのように服用すべきかを示す情報</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationstatement-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationstatement-injection.xlsx
@@ -501,7 +501,7 @@
   </si>
   <si>
     <t>このインスタンスが外部から参照されるために使われるIDである。それ以外に任意のIDを付与してもよい。
-このIDは業務手順によって定められた処方オーダーに対して、直接的なURL参照が適切でない場合も含めて関連付けるために使われる。この業務手順のIDは実施者によって割り当てられたものであり、リソースが更新されたりサーバからサーバに転送されたとしても固定のものとして存続する。</t>
+このIDは業務手順によって定められた処方オーダーに対して、直接的なURL参照が適切でない場合も含めて関連付けるために使われる。この業務手順のIDは実施者によって割り当てられたものであり、リソースが更新されたりサーバーからサーバーに転送されたとしても固定のものとして存続する。</t>
   </si>
   <si>
     <t>これは業務IDであって、リソースに対するIDではない。</t>
